--- a/salon_forms/005_lip_blush_consultation_form--salon_forms.xlsx
+++ b/salon_forms/005_lip_blush_consultation_form--salon_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -2695,29 +2695,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>shellfish</t>
+          <t>tree_nuts</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Shellfish</t>
+          <t>Tree nuts</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>medications_allergies_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>tree_nuts</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tree nuts</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2729,29 +2729,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>medications_allergies_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2763,29 +2763,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>client_consent_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2797,27 +2797,10 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>client_consent_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
         <is>
           <t>False</t>
         </is>
